--- a/模板.xlsx
+++ b/模板.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>尼姑.mp3</t>
+          <t>涨粉配音-男.mp3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>属龙人不想发财就划走，再忙也要听一听。师傅今天送你四句话，划走你就后悔一辈子。福星照耀心欢畅，贵人相助步步高，前途光明一路顺，富贵安康乐无边。属龙人横财迸发，遍地黄金，腰缠万贯，本该在今年财源滚滚，日进斗金，但今年是二零二五青蛇年，也是双春闰六月的年份，老话讲得好，一年打两春，黄土变成金。八月过后，属龙人将会碰见三件大事，务必听好，尤其最后一件格外重要，把握好的话，九月开始走上坡路，还请认真听完，提前做好准备。第一是步入金九银十的金九月属龙人将会遇见一个机遇，做事水到渠成。第二是八月二十三号处暑节气过后，你会遇到一个人，他是你今年最大的贵人，不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属龙人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱，在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月七号白露节气前把这个老师傅祝福过的五行黄财神手串请回去，男戴左手女戴右手，这是有讲究的，五行黄财神手串是根据传统生肖文化为属龙人设计的，只要能保持虔程之心便可得到黄财神的祝福，并且手串上有六字真言的加持，两者相辅相合，和谐共荣，让你挣得多也会存得住，逆转运势，聚拢财气运，虔程佩戴，避开身边压着你财运的人和事，驱邪避凶，镇宅纳福，身边小人无处遁行，做事水到渠成，翻身上岸，从此一发不可收拾，再忙也要请回去。</t>
+          <t>属鼠的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六零年、七二年、八四年的富贵鼠，属鼠人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属鼠人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属鼠人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C:\Users\Administrator\Desktop\2025-08-26\ZL\尼姑_属龙人不想发财就_213531.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属鼠的九月要出大_120037.wav</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-03</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>尼姑.mp3</t>
+          <t>涨粉配音-男.mp3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>属蛇人不想发财就划走，再忙也要听一听。师傅今天送你四句话，划走你就后悔一辈子。福星照耀心欢畅，贵人相助步步高，前途光明一路顺，富贵安康乐无边。属蛇人横财迸发，遍地黄金，腰缠万贯，本该在今年财源滚滚，日进斗金，但今年是二零二五青蛇年，也是双春闰六月的年份，老话讲得好，一年打两春，黄土变成金。八月过后，属蛇人将会碰见三件大事，务必听好，尤其最后一件格外重要，把握好的话，九月开始走上坡路，还请认真听完，提前做好准备。第一是步入金九银十的金九月属蛇人将会遇见一个机遇，做事水到渠成。第二是八月二十三号处暑节气过后，你会遇到一个人，他是你今年最大的贵人，不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属蛇人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱，在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月七号白露节气前把这个老师傅祝福过的五行黄财神手串请回去，男戴左手女戴右手，这是有讲究的，五行黄财神手串是根据传统生肖文化为属蛇人设计的，只要能保持虔程之心便可得到黄财神的祝福，并且手串上有六字真言的加持，两者相辅相合，和谐共荣，让你挣得多也会存得住，逆转运势，聚拢财气运，虔程佩戴，避开身边压着你财运的人和事，驱邪避凶，镇宅纳福，身边小人无处遁行，做事水到渠成，翻身上岸，从此一发不可收拾，再忙也要请回去。</t>
+          <t>属牛的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六一年、七三年、八五年的富贵牛，属牛人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属牛人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属牛人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C:\Users\Administrator\Desktop\2025-08-26\ZL\尼姑_属蛇人不想发财就_213636.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属牛的九月要出大_120129.wav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-03</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>尼姑.mp3</t>
+          <t>涨粉配音-男.mp3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>属马人不想发财就划走，再忙也要听一听。师傅今天送你四句话，划走你就后悔一辈子。福星照耀心欢畅，贵人相助步步高，前途光明一路顺，富贵安康乐无边。属马人横财迸发，遍地黄金，腰缠万贯，本该在今年财源滚滚，日进斗金，但今年是二零二五青蛇年，也是双春闰六月的年份，老话讲得好，一年打两春，黄土变成金。八月过后，属马人将会碰见三件大事，务必听好，尤其最后一件格外重要，把握好的话，九月开始走上坡路，还请认真听完，提前做好准备。第一是步入金九银十的金九月属马人将会遇见一个机遇，做事水到渠成。第二是八月二十三号处暑节气过后，你会遇到一个人，他是你今年最大的贵人，不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属马人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱，在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月七号白露节气前把这个老师傅祝福过的五行黄财神手串请回去，男戴左手女戴右手，这是有讲究的，五行黄财神手串是根据传统生肖文化为属马人设计的，只要能保持虔程之心便可得到黄财神的祝福，并且手串上有六字真言的加持，两者相辅相合，和谐共荣，让你挣得多也会存得住，逆转运势，聚拢财气运，虔程佩戴，避开身边压着你财运的人和事，驱邪避凶，镇宅纳福，身边小人无处遁行，做事水到渠成，翻身上岸，从此一发不可收拾，再忙也要请回去。</t>
+          <t>属虎的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六二年、七四年、八六年的富贵虎，属虎人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属虎人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属虎人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">错误: </t>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属虎的九月要出大_120221.wav</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-03</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>尼姑.mp3</t>
+          <t>涨粉配音-男.mp3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>属羊人不想发财就划走，再忙也要听一听。师傅今天送你四句话，划走你就后悔一辈子。福星照耀心欢畅，贵人相助步步高，前途光明一路顺，富贵安康乐无边。属羊人横财迸发，遍地黄金，腰缠万贯，本该在今年财源滚滚，日进斗金，但今年是二零二五青蛇年，也是双春闰六月的年份，老话讲得好，一年打两春，黄土变成金。八月过后，属羊人将会碰见三件大事，务必听好，尤其最后一件格外重要，把握好的话，九月开始走上坡路，还请认真听完，提前做好准备。第一是步入金九银十的金九月属羊人将会遇见一个机遇，做事水到渠成。第二是八月二十三号处暑节气过后，你会遇到一个人，他是你今年最大的贵人，不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属羊人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱，在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月七号白露节气前把这个老师傅祝福过的五行黄财神手串请回去，男戴左手女戴右手，这是有讲究的，五行黄财神手串是根据传统生肖文化为属羊人设计的，只要能保持虔程之心便可得到黄财神的祝福，并且手串上有六字真言的加持，两者相辅相合，和谐共荣，让你挣得多也会存得住，逆转运势，聚拢财气运，虔程佩戴，避开身边压着你财运的人和事，驱邪避凶，镇宅纳福，身边小人无处遁行，做事水到渠成，翻身上岸，从此一发不可收拾，再忙也要请回去。</t>
+          <t>属兔的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六三年、七五年、八七年的富贵兔，属兔人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属兔人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属兔人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>错误: [WinError 10061] 由于目标计算机积极拒绝，无法连接。</t>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属兔的九月要出大_120310.wav</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-03</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>尼姑.mp3</t>
+          <t>涨粉配音-男.mp3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>属猴人不想发财就划走，再忙也要听一听。师傅今天送你四句话，划走你就后悔一辈子。福星照耀心欢畅，贵人相助步步高，前途光明一路顺，富贵安康乐无边。属猴人横财迸发，遍地黄金，腰缠万贯，本该在今年财源滚滚，日进斗金，但今年是二零二五青蛇年，也是双春闰六月的年份，老话讲得好，一年打两春，黄土变成金。八月过后，属猴人将会碰见三件大事，务必听好，尤其最后一件格外重要，把握好的话，九月开始走上坡路，还请认真听完，提前做好准备。第一是步入金九银十的金九月属猴人将会遇见一个机遇，做事水到渠成。第二是八月二十三号处暑节气过后，你会遇到一个人，他是你今年最大的贵人，不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属猴人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱，在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月七号白露节气前把这个老师傅祝福过的五行黄财神手串请回去，男戴左手女戴右手，这是有讲究的，五行黄财神手串是根据传统生肖文化为属猴人设计的，只要能保持虔程之心便可得到黄财神的祝福，并且手串上有六字真言的加持，两者相辅相合，和谐共荣，让你挣得多也会存得住，逆转运势，聚拢财气运，虔程佩戴，避开身边压着你财运的人和事，驱邪避凶，镇宅纳福，身边小人无处遁行，做事水到渠成，翻身上岸，从此一发不可收拾，再忙也要请回去。</t>
+          <t>属龙的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六四年、七六年、八八年的富贵龙，属龙人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属龙人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属龙人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>错误: [WinError 10061] 由于目标计算机积极拒绝，无法连接。</t>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属龙的九月要出大_120400.wav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-03</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>尼姑.mp3</t>
+          <t>涨粉配音-男.mp3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>属鸡人不想发财就划走，再忙也要听一听。师傅今天送你四句话，划走你就后悔一辈子。福星照耀心欢畅，贵人相助步步高，前途光明一路顺，富贵安康乐无边。属鸡人横财迸发，遍地黄金，腰缠万贯，本该在今年财源滚滚，日进斗金，但今年是二零二五青蛇年，也是双春闰六月的年份，老话讲得好，一年打两春，黄土变成金。八月过后，属鸡人将会碰见三件大事，务必听好，尤其最后一件格外重要，把握好的话，九月开始走上坡路，还请认真听完，提前做好准备。第一是步入金九银十的金九月属鸡人将会遇见一个机遇，做事水到渠成。第二是八月二十三号处暑节气过后，你会遇到一个人，他是你今年最大的贵人，不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属鸡人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱，在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月七号白露节气前把这个老师傅祝福过的五行黄财神手串请回去，男戴左手女戴右手，这是有讲究的，五行黄财神手串是根据传统生肖文化为属鸡人设计的，只要能保持虔程之心便可得到黄财神的祝福，并且手串上有六字真言的加持，两者相辅相合，和谐共荣，让你挣得多也会存得住，逆转运势，聚拢财气运，虔程佩戴，避开身边压着你财运的人和事，驱邪避凶，镇宅纳福，身边小人无处遁行，做事水到渠成，翻身上岸，从此一发不可收拾，再忙也要请回去。</t>
+          <t>属蛇的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六五年、七七年、八九年的富贵蛇，属蛇人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属蛇人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属蛇人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>错误: [WinError 10061] 由于目标计算机积极拒绝，无法连接。</t>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属蛇的九月要出大_120449.wav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-03</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>尼姑.mp3</t>
+          <t>涨粉配音-男.mp3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>属狗人不想发财就划走，再忙也要听一听。师傅今天送你四句话，划走你就后悔一辈子。福星照耀心欢畅，贵人相助步步高，前途光明一路顺，富贵安康乐无边。属狗人横财迸发，遍地黄金，腰缠万贯，本该在今年财源滚滚，日进斗金，但今年是二零二五青蛇年，也是双春闰六月的年份，老话讲得好，一年打两春，黄土变成金。八月过后，属狗人将会碰见三件大事，务必听好，尤其最后一件格外重要，把握好的话，九月开始走上坡路，还请认真听完，提前做好准备。第一是步入金九银十的金九月属狗人将会遇见一个机遇，做事水到渠成。第二是八月二十三号处暑节气过后，你会遇到一个人，他是你今年最大的贵人，不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属狗人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱，在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月七号白露节气前把这个老师傅祝福过的五行黄财神手串请回去，男戴左手女戴右手，这是有讲究的，五行黄财神手串是根据传统生肖文化为属狗人设计的，只要能保持虔程之心便可得到黄财神的祝福，并且手串上有六字真言的加持，两者相辅相合，和谐共荣，让你挣得多也会存得住，逆转运势，聚拢财气运，虔程佩戴，避开身边压着你财运的人和事，驱邪避凶，镇宅纳福，身边小人无处遁行，做事水到渠成，翻身上岸，从此一发不可收拾，再忙也要请回去。</t>
+          <t>属马的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六六年、七八年、九零年的富贵马，属马人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属马人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属马人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>错误: [WinError 10061] 由于目标计算机积极拒绝，无法连接。</t>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属马的九月要出大_120541.wav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-03</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>尼姑.mp3</t>
+          <t>涨粉配音-男.mp3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>属猪人不想发财就划走，再忙也要听一听。师傅今天送你四句话，划走你就后悔一辈子。福星照耀心欢畅，贵人相助步步高，前途光明一路顺，富贵安康乐无边。属猪人横财迸发，遍地黄金，腰缠万贯，本该在今年财源滚滚，日进斗金，但今年是二零二五青蛇年，也是双春闰六月的年份，老话讲得好，一年打两春，黄土变成金。八月过后，属猪人将会碰见三件大事，务必听好，尤其最后一件格外重要，把握好的话，九月开始走上坡路，还请认真听完，提前做好准备。第一是步入金九银十的金九月属猪人将会遇见一个机遇，做事水到渠成。第二是八月二十三号处暑节气过后，你会遇到一个人，他是你今年最大的贵人，不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属猪人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱，在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月七号白露节气前把这个老师傅祝福过的五行黄财神手串请回去，男戴左手女戴右手，这是有讲究的，五行黄财神手串是根据传统生肖文化为属猪人设计的，只要能保持虔程之心便可得到黄财神的祝福，并且手串上有六字真言的加持，两者相辅相合，和谐共荣，让你挣得多也会存得住，逆转运势，聚拢财气运，虔程佩戴，避开身边压着你财运的人和事，驱邪避凶，镇宅纳福，身边小人无处遁行，做事水到渠成，翻身上岸，从此一发不可收拾，再忙也要请回去。</t>
+          <t>属羊的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六七年、七九年、九一年的富贵羊，属羊人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属羊人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属羊人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1327,12 +1327,140 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>错误: [WinError 10061] 由于目标计算机积极拒绝，无法连接。</t>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属羊的九月要出大_120631.wav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ZL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>涨粉配音-男.mp3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>属猴的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六八年、八零年、九二年的富贵猴，属猴人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属猴人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属猴人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>曾老.mp4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属猴的九月要出大_120722.wav</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ZL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>涨粉配音-男.mp3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>属鸡的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六九年、八一年、九三年的富贵鸡，属鸡人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属鸡人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属鸡人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>曾老.mp4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属鸡的九月要出大_120812.wav</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ZL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>涨粉配音-男.mp3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>属狗的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其五八年、七零年、八二年的富贵狗，属狗人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属狗人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属狗人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>曾老.mp4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属狗的九月要出大_120902.wav</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ZL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>涨粉配音-男.mp3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>属猪的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其五九年、七一年、八三年的富贵猪，属猪人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属猪人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属猪人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>曾老.mp4</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属猪的九月要出大_120952.wav</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
         </is>
       </c>
     </row>

--- a/模板.xlsx
+++ b/模板.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>属鼠的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六零年、七二年、八四年的富贵鼠，属鼠人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属鼠人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属鼠人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属鼠的不想发财就划走，再忙也要听一听，特别是六零、七二和八四年的富贵鼠，划走，你就后悔一辈子。中元节过后一定要注意了，属鼠人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属鼠人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属鼠人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属鼠人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属鼠人的本命守护佛千手观音会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属鼠的九月要出大_120037.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属鼠的不想发财就_140336.wav</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>属牛的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六一年、七三年、八五年的富贵牛，属牛人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属牛人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属牛人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属牛的不想发财就划走，再忙也要听一听，特别是六一、七三和八五年的富贵牛，划走，你就后悔一辈子。中元节过后一定要注意了，属牛人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属牛人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属牛人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属牛人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属牛人的本命守护佛虚空葬菩萨会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属牛的九月要出大_120129.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属牛的不想发财就_140441.wav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>属虎的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六二年、七四年、八六年的富贵虎，属虎人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属虎人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属虎人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属虎的不想发财就划走，再忙也要听一听，特别是六二、七四和八六年的富贵虎，划走，你就后悔一辈子。中元节过后一定要注意了，属虎人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属虎人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属虎人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属虎人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属虎人的本命守护佛虚空葬菩萨会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属虎的九月要出大_120221.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属虎的不想发财就_140546.wav</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>属兔的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六三年、七五年、八七年的富贵兔，属兔人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属兔人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属兔人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属兔的不想发财就划走，再忙也要听一听，特别是六三、七五和八七年的富贵兔，划走，你就后悔一辈子。中元节过后一定要注意了，属兔人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属兔人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属兔人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属兔人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属兔人的本命守护佛文殊菩萨会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属兔的九月要出大_120310.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属兔的不想发财就_140651.wav</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>属龙的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六四年、七六年、八八年的富贵龙，属龙人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属龙人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属龙人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属龙的不想发财就划走，再忙也要听一听，特别是六四、七六和八八年的富贵龙，划走，你就后悔一辈子。中元节过后一定要注意了，属龙人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属龙人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属龙人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属龙人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属龙人的本命守护佛普贤菩萨会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属龙的九月要出大_120400.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属龙的不想发财就_140755.wav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>属蛇的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六五年、七七年、八九年的富贵蛇，属蛇人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属蛇人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属蛇人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属蛇的不想发财就划走，再忙也要听一听，特别是六五、七七和八九年的富贵蛇，划走，你就后悔一辈子。中元节过后一定要注意了，属蛇人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属蛇人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属蛇人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属蛇人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属蛇人的本命守护佛普贤菩萨会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属蛇的九月要出大_120449.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属蛇的不想发财就_140900.wav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>属马的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六六年、七八年、九零年的富贵马，属马人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属马人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属马人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属马的不想发财就划走，再忙也要听一听，特别是六六、七八和九零年的富贵马，划走，你就后悔一辈子。中元节过后一定要注意了，属马人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属马人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属马人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属马人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属马人的本命守护佛大势至菩萨会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属马的九月要出大_120541.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属马的不想发财就_141004.wav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>属羊的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六七年、七九年、九一年的富贵羊，属羊人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属羊人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属羊人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属羊的不想发财就划走，再忙也要听一听，特别是六七、七九和九一年的富贵羊，划走，你就后悔一辈子。中元节过后一定要注意了，属羊人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属羊人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属羊人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属羊人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属羊人的本命守护佛大日如来会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属羊的九月要出大_120631.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属羊的不想发财就_141107.wav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>属猴的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六八年、八零年、九二年的富贵猴，属猴人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属猴人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属猴人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属猴的不想发财就划走，再忙也要听一听，特别是六八、八零和九二年的富贵猴，划走，你就后悔一辈子。中元节过后一定要注意了，属猴人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属猴人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属猴人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属猴人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属猴人的本命守护佛大日如来会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属猴的九月要出大_120722.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属猴的不想发财就_141213.wav</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>属鸡的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其六九年、八一年、九三年的富贵鸡，属鸡人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属鸡人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属鸡人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属鸡的不想发财就划走，再忙也要听一听，特别是六九、八一和九三年的富贵鸡，划走，你就后悔一辈子。中元节过后一定要注意了，属鸡人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属鸡人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属鸡人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属鸡人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属鸡人的本命守护佛不动尊菩萨会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属鸡的九月要出大_120812.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属鸡的不想发财就_141318.wav</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>属狗的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其五八年、七零年、八二年的富贵狗，属狗人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属狗人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属狗人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属狗的不想发财就划走，再忙也要听一听，特别是七零、八二和九四年的富贵狗，划走，你就后悔一辈子。中元节过后一定要注意了，属狗人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属狗人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属狗人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属狗人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属狗人的本命守护佛阿弥陀佛会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属狗的九月要出大_120902.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属狗的不想发财就_141425.wav</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>属猪的九月要出大事，走错半步，家财散尽财散浮消，我这并不是在咒你，听不听由你，尤其五九年、七一年、八三年的富贵猪，属猪人从二零一九年到二零二五这几年，是不是总感觉不顺，一有点钱就有事发生，身体和事业也没有好的进展，不过从二零二五年九月开始，将是你三十年难一遇的翻身好时机，因为二零二五年是金蛇年，双春和闰六月撞一起，老话说，春来蛇行运难平，这会牵动属猪人后半生财路，你今年本该顺风顺水，可是有个眼红的家伙藏在暗处盯着你的好运下手，他是你今年最大的敌人，你要时刻提防他会破坏你的财运，甚至还会让你花几十万的冤枉钱，师傅教你个方法，一定要照做，如果没有用，天打雷劈，跪下来给你道歉，倘若有用，你只需要和我说声谢谢就可以了，记住，必须赶在秋分节气之前，准确点来说，也就是九月二十三号前把这个一百零八岁老师傅祝福过的红纱葫芦钱袋子请回去，随身携带或者放在入户门两侧，这是有讲究的，老话讲得好，宝葫芦中藏瑞气，福禄双全聚华堂，仙藤蔓绕招祥运，金玉满堂喜安康，红砂葫芦根据传统文化专为属猪人设计的，葫芦谐音福禄，红砂寓意互佑，两者相合，可助你福禄双全，远离小人，青蛇年戴红砂葫芦，能帮你避开压着你财运的人，镇宅纳福逆转运势，聚拢财气运，让你买豪车住别墅，谁也阻挡不了你走上坡路，记住，今天你能刷到就是你的福气，再忙也要请回去。</t>
+          <t>属猪的不想发财就划走，再忙也要听一听，特别是七一、八三和九五年的富贵猪，划走，你就后悔一辈子。中元节过后一定要注意了，属猪人将会遇到两喜一灾三件大事，尤其是最后一件，你一定要听好了。第一是步入金九银十的金九月属猪人将会遇见一个机遇，做事水到渠成。第二是中元节气过后，你会遇到一个人，他是你今年最大的贵人不但会助您度过难关，还会帮您踢走小人，踢走一切不好的。第三是来到蛇年乙酉月，天干为乙，地支为酉，正值五行金能量的顶峰，这将会是属猪人几十年难一遇的翻身好时机，运势时来运转，但此时你一定要留心身边一个人，他是你今年最大的敌人，要时刻提防，因为他不但会常常嫉妒你的好，容易破坏你的运，还会给你带来无妄之灾，致使你痛失一辈子的血汗钱。在此，师傅教你一个破局的秘密，倘若没用，给你下跪道歉，记住，一定要在九月二十三号秋分节气前把这个茅山老先生开过的红纱本命佛护身手串请回去，男带左手，女带右手，或者放在一件不常穿的衣服里，这是有讲究的，本命佛护身手串是根据民间的立法民俗生肖理论专为属猪人设计的，红砂寓意着吉祥顺遂，再加上金刚护身符，已达到相辅相成，和谐共荣，请回去之后全程佩戴，属猪人的本命守护佛阿弥陀佛会帮你避开压着你财运的人，得贵人相助，做事水到渠成，度过财富难关，一生财富不断，记住，今天你能刷到就是好运的开始，证明你匹极泰来要翻身了，这也许就是大数据神奇之所在，一定要把握属于你的好运，再忙也要请回去。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>F:\workspace\python\outputs\2025-09-03\ZL\涨粉配音-男_属猪的九月要出大_120952.wav</t>
+          <t>F:\workspace\python\outputs\2025-09-08\ZL\涨粉配音-男_属猪的不想发财就_141529.wav</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
